--- a/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
+++ b/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_第9期計画における給付適正化の記載" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_国が求める記載事項との対照" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_第10期での位置づけ（3案）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_主要3事業の毎年度の定量目標（受託者案）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_主要3事業の毎年度の定量目標" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_財政調整交付金への影響" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_進捗管理の手引きに基づく整理" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_介護SCRの活用案" sheetId="8" state="visible" r:id="rId8"/>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCRデータ）を読み込み、第10期計画への反映を要する事項を整理しました。ご指示により、本表の内容は計画素案の本文には反映していません。計画素案に入れるかどうかは、第9期計画の体裁を勘案して協議のうえ決定します。</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCRデータ）を読み込み、第10期計画への反映を要する事項を整理しました。令和8年9月10日、給付適正化計画の位置づけは案Bを採用し計画素案を更新するご指示をいただきました。介護SCRと進捗管理の手引きの引用は、計画素案に入れるかどうかを引き続き協議いただく事項です。</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>本表に示す案は、いずれも受託者の案です。計画素案の本文には反映していません。第9期計画の体裁との関係を協議したうえで、反映する範囲を決めていただきます。</t>
+          <t>本表に示す案は、受託者の案です。第9期計画の体裁との関係を協議したうえで、計画素案に反映する範囲を決めていただきます。令和8年9月10日に決定をいただいた範囲は反映済みです。</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -598,12 +598,12 @@
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>反映しなかったもの</t>
+          <t>計画素案に反映したもの</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>①給付適正化計画の位置づけ（03シート）、②主要3事業の毎年度の定量目標（04シート）、③介護SCRの図表（07シート）、④進捗管理の手引きの引用（06シート）。いずれも計画素案には入れていません。</t>
+          <t>給付適正化計画の位置づけ（03シートの案B）と主要3事業の毎年度の定量目標（04シート）。令和8年9月10日に案Bの採用と素案の更新のご指示をいただいたため、第5章 基本目標5（3）に反映しました。あわせて第1章第2節に法第117条第2項第3号・第4号の記載を、資料5に指針・手引き・評価指標を加えました。</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -614,12 +614,12 @@
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>既に反映したもの</t>
+          <t>計画素案に反映していないもの</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）への5件の追加と北海道への依頼の組立ての変更。実施要領は計画素案とは別の成果品であり、国の指針の内容をそのまま反映するものであるため、先に反映しています（08シートNo.3）。</t>
+          <t>①介護SCRの図表（07シート）、②進捗管理の手引きの引用（06シート）。いずれもご判断をお待ちしています（08シートNo.4・No.5）。</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -630,51 +630,51 @@
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>確認事項として起票したもの</t>
+          <t>既に反映したもの</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>財政調整交付金への主要3事業の勘案（05シート）。保険料の算定に影響し得るため、業務工程管理表の確認事項一覧に加えています。</t>
+          <t>ケアプラン点検実施要領（案）への5件の追加と北海道への依頼の組立ての変更。実施要領は計画素案とは別の成果品であり、国の指針の内容をそのまま反映するものであるため、先に反映しています（08シートNo.3）。</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>確認事項として起票したもの</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>財政調整交付金への主要3事業の勘案（05シート）。保険料の算定に影響し得るため、業務工程管理表の確認事項一覧に加えています。</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>【シートの構成】</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>01_第9期計画における給付適正化の記載</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>ご指摘のとおり、第9期計画には記載がありました。名称は「介護給付適正化計画」ではありません。</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>02_国が求める記載事項との対照</t>
+          <t>01_第9期計画における給付適正化の記載</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>令和5年9月12日の指針が求める事項と、第9期計画・第10期計画素案の状況を対照します。</t>
+          <t>ご指摘のとおり、第9期計画には記載がありました。名称は「介護給付適正化計画」ではありません。</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
@@ -685,12 +685,12 @@
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>03_第10期での位置づけ（3案）</t>
+          <t>02_国が求める記載事項との対照</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>節として置く案・施策として置く案・別冊とする案を比較します。他団体の例も併記します。</t>
+          <t>令和5年9月12日の指針が求める事項と、第9期計画・第10期計画素案の状況を対照します。</t>
         </is>
       </c>
       <c r="D13" s="4" t="n"/>
@@ -701,12 +701,12 @@
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>04_主要3事業の毎年度の定量目標（受託者案）</t>
+          <t>03_第10期での位置づけ（3案）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>指針が求める「事業ごとの毎年度の定量的な目標」の案です。</t>
+          <t>節として置く案・施策として置く案・別冊とする案を比較します。他団体の例も併記します。</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
@@ -717,12 +717,12 @@
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>05_財政調整交付金への影響</t>
+          <t>04_主要3事業の毎年度の定量目標</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>指針は、財政調整交付金の算定に当たって主要3事業の取組状況を勘案するとしています。</t>
+          <t>指針が求める「事業ごとの毎年度の定量的な目標」です。計画素案 第5章 基本目標5（3）に反映しました。</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
@@ -733,12 +733,12 @@
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>06_進捗管理の手引きに基づく整理</t>
+          <t>05_財政調整交付金への影響</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>平成30年の手引きと当方の3層構造との対応です。</t>
+          <t>指針は、財政調整交付金の算定に当たって主要3事業の取組状況を勘案するとしています。</t>
         </is>
       </c>
       <c r="D16" s="4" t="n"/>
@@ -749,12 +749,12 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>07_介護SCRの活用案</t>
+          <t>06_進捗管理の手引きに基づく整理</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>受領した介護SCRを計画のどこで使えるかの整理です。</t>
+          <t>平成30年の手引きと当方の3層構造との対応です。</t>
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
@@ -765,27 +765,43 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>08_確認事項</t>
+          <t>07_介護SCRの活用案</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ご判断をお願いする事項の一覧です。</t>
+          <t>受領した介護SCRを計画のどこで使えるかの整理です。</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
     </row>
-    <row r="20" ht="39" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>08_確認事項</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>ご判断をお願いする事項の一覧です。</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+    </row>
+    <row r="21" ht="39" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>【前回のご報告の訂正】令和8年9月10日のご報告において、「当方の計画素案を検索したところ『市町村介護給付適正化計画』という位置づけの記載はない」旨をお伝えしましたが、第9期計画には施策4-3「介護給付費の適正化（第6期給付適正化計画）」として記載がありました。「介護給付適正化計画」という語で検索したため見落としたものです。01シートに正しい状況を整理しています。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>【他団体の資料の扱い】03シートに他団体の例を併記していますが、記載の借用は行っていません。位置づけの選択肢を比較するための材料としてのみ用いており、当該団体名は協議の場に限りお示しするものです。</t>
         </is>
@@ -794,11 +810,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1342,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1434,7 +1450,8 @@
     <row r="6" ht="110" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B
+【採用】</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1498,14 +1515,22 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>【受託者の案】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
+          <t>【受託者の案と決定】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>案Bを基本とし、施策名を「介護給付費の適正化（第7期給付適正化計画）」として第9期の体裁を継承することを受託者の案とします。理由は次の3点です。
+          <t>令和8年9月10日、案Bの採用と計画素案の更新のご指示をいただきました。計画素案 第5章 基本目標5（3）に【介護給付費の適正化（第7期給付適正化計画）】の項を設け、法第117条第2項第3号・第4号に対応する記載であることと、第9期計画の施策4-3を継承することを明記しました。毎年度の定量的な目標は、北海道への報告が求められるため同項に表として掲げています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>以下は決定前の受託者の案です。記録として残します。
+案Bを基本とし、施策名を「介護給付費の適正化（第7期給付適正化計画）」として第9期の体裁を継承することを受託者の案とします。理由は次の3点です。
 ① 指針が求めるのは施策と目標であり、節や章の設置ではないこと。
 ② 第9期計画の体裁を維持するという本業務の方針に沿うこと。
 ③ 主要3事業の詳細はケアプラン点検実施要領及び実施要領に準じて作成する要領で定めることとし、計画本文は施策と目標にとどめられること。
@@ -1513,17 +1538,18 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>案Aを採る場合は、第10期計画の章立てが第9期と変わります。第2章第2節に構成町別の状況を加えたこと、第6章第4節に日常生活圏域ごとの必要利用定員総数を加えたことと併せて、章立ての変更として一括してお諮りするのが適当と考えます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A12:F12"/>
@@ -1553,14 +1579,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主要3事業の毎年度の定量的な目標（受託者案）</t>
+          <t>主要3事業の毎年度の定量的な目標（計画素案に反映済み）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>指針は、事業ごとに令和9年度から令和11年度までの毎年度ごとの定量的な目標を設定し、都道府県に報告することを求めています。ケアプラン点検については実施要領で定めた値、他の2事業については受託者の案です。</t>
+          <t>指針は、事業ごとに令和9年度から令和11年度までの毎年度ごとの定量的な目標を設定し、都道府県に報告することを求めています。ケアプラン点検については実施要領で定めた値、他の2事業については受託者の案です。令和8年9月10日のご指示により、本表の内容を計画素案 第5章 基本目標5（3）に掲げました。</t>
         </is>
       </c>
     </row>
@@ -3479,27 +3505,27 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ</t>
+          <t>給付適正化計画の位置づけ【決定済】</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>03シートの3案のうち、いずれによるか。受託者の案は案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）。案Aを採る場合は章立ての変更となるため、他の章立ての変更と併せてお諮りする。</t>
+          <t>令和8年9月10日、案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）の採用と、計画素案の更新のご指示をいただいた。第5章 基本目標5（3）に反映済み。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>了承済</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3535,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>毎年度の定量的な目標の記載場所</t>
+          <t>毎年度の定量的な目標の記載場所【反映済】</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>04シートの目標を計画本文に表として掲げるか、資料編に置くか、実施要領にとどめるか。北海道への報告が求められるため、所在を明らかにしておく必要がある。</t>
+          <t>北海道への報告が求められるため、04シートの目標を計画素案 第5章 基本目標5（3）に表として掲げた。資料編に移す場合は改めてご指示いただきたい。認定調査の点検件数・住宅改修の点検件数・福祉用具購入貸与調査の件数は［要協議］としている。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>計画素案 第5章・資料編</t>
+          <t>計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">

--- a/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
+++ b/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
@@ -2086,12 +2086,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>第9期計画は7.375％</t>
+          <t>第9期計画は7.3755％（E÷（A＋総合事業費）の実数）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>将来推計 第3段階は「第9期計画と同水準」として7.375％を置いている</t>
+          <t>将来推計 第3段階は「第9期計画と同水準」として7.3755％を置いている。7.375％に丸めると49,113円合わない</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
